--- a/data/subjects.xlsx
+++ b/data/subjects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Noa_project\github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F61F60-0BDC-47FD-9AEF-17855FBF54C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B1EA06-8AF9-4766-91D9-BA0D8ADAFBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="181">
   <si>
     <t>subject</t>
   </si>
@@ -570,6 +570,18 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Male</t>
   </si>
 </sst>
 </file>
@@ -957,7 +969,12 @@
       <c r="K1" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="1"/>
+      <c r="L1" t="s">
+        <v>177</v>
+      </c>
+      <c r="M1" t="s">
+        <v>178</v>
+      </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -997,7 +1014,12 @@
       <c r="K2">
         <v>-19.659984789007002</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="L2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M2">
+        <v>36.142996320000002</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="3"/>
@@ -1037,7 +1059,12 @@
       <c r="K3">
         <v>-14.8249365668533</v>
       </c>
-      <c r="M3" s="2"/>
+      <c r="L3" t="s">
+        <v>180</v>
+      </c>
+      <c r="M3">
+        <v>44.373144779999997</v>
+      </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="3"/>
@@ -1077,7 +1104,12 @@
       <c r="K4">
         <v>-12.4176752664138</v>
       </c>
-      <c r="M4" s="2"/>
+      <c r="L4" t="s">
+        <v>180</v>
+      </c>
+      <c r="M4">
+        <v>44.373144779999997</v>
+      </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="3"/>
@@ -1117,7 +1149,12 @@
       <c r="K5">
         <v>-20.295260074696198</v>
       </c>
-      <c r="M5" s="2"/>
+      <c r="L5" t="s">
+        <v>180</v>
+      </c>
+      <c r="M5">
+        <v>25.974523779999998</v>
+      </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="3"/>
@@ -1157,7 +1194,12 @@
       <c r="K6">
         <v>-31.124293882925201</v>
       </c>
-      <c r="M6" s="2"/>
+      <c r="L6" t="s">
+        <v>179</v>
+      </c>
+      <c r="M6">
+        <v>25.774542480000001</v>
+      </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3"/>
@@ -1197,7 +1239,12 @@
       <c r="K7">
         <v>-14.94216022</v>
       </c>
-      <c r="M7" s="2"/>
+      <c r="L7" t="s">
+        <v>180</v>
+      </c>
+      <c r="M7">
+        <v>37.254700640000003</v>
+      </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="3"/>
@@ -1237,7 +1284,12 @@
       <c r="K8">
         <v>-33.20516559</v>
       </c>
-      <c r="M8" s="2"/>
+      <c r="L8" t="s">
+        <v>179</v>
+      </c>
+      <c r="M8">
+        <v>41.750343950000001</v>
+      </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="3"/>
@@ -1277,7 +1329,12 @@
       <c r="K9">
         <v>-26.774648345634802</v>
       </c>
-      <c r="M9" s="2"/>
+      <c r="L9" t="s">
+        <v>179</v>
+      </c>
+      <c r="M9">
+        <v>56.263988990000001</v>
+      </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="3"/>
@@ -1317,7 +1374,12 @@
       <c r="K10">
         <v>-10.604299369284499</v>
       </c>
-      <c r="M10" s="2"/>
+      <c r="L10" t="s">
+        <v>179</v>
+      </c>
+      <c r="M10">
+        <v>51.729900909999998</v>
+      </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="3"/>
@@ -1357,7 +1419,12 @@
       <c r="K11">
         <v>-22.202122960000001</v>
       </c>
-      <c r="M11" s="2"/>
+      <c r="L11" t="s">
+        <v>180</v>
+      </c>
+      <c r="M11">
+        <v>63.924652799999997</v>
+      </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="3"/>
@@ -1397,7 +1464,12 @@
       <c r="K12">
         <v>0.88350284228286002</v>
       </c>
-      <c r="M12" s="2"/>
+      <c r="L12" t="s">
+        <v>179</v>
+      </c>
+      <c r="M12">
+        <v>57.000485980000001</v>
+      </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="3"/>
@@ -1437,7 +1509,12 @@
       <c r="K13">
         <v>-29.591136514331701</v>
       </c>
-      <c r="M13" s="2"/>
+      <c r="L13" t="s">
+        <v>179</v>
+      </c>
+      <c r="M13">
+        <v>52.587093959999997</v>
+      </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="3"/>
@@ -1477,7 +1554,12 @@
       <c r="K14">
         <v>-20.0485572948133</v>
       </c>
-      <c r="M14" s="2"/>
+      <c r="L14" t="s">
+        <v>179</v>
+      </c>
+      <c r="M14">
+        <v>52.587093959999997</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="3"/>
@@ -1517,7 +1599,12 @@
       <c r="K15">
         <v>-5.9623587122013202</v>
       </c>
-      <c r="M15" s="2"/>
+      <c r="L15" t="s">
+        <v>179</v>
+      </c>
+      <c r="M15">
+        <v>44.34325596</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="3"/>
@@ -1557,7 +1644,12 @@
       <c r="K16">
         <v>-33.432038488626901</v>
       </c>
-      <c r="M16" s="2"/>
+      <c r="L16" t="s">
+        <v>179</v>
+      </c>
+      <c r="M16">
+        <v>57.575560529999997</v>
+      </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="3"/>
@@ -1597,7 +1689,12 @@
       <c r="K17">
         <v>-20.231694788385301</v>
       </c>
-      <c r="M17" s="2"/>
+      <c r="L17" t="s">
+        <v>179</v>
+      </c>
+      <c r="M17">
+        <v>39.316230539999999</v>
+      </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="3"/>
@@ -1637,7 +1734,12 @@
       <c r="K18">
         <v>-23.6060426064466</v>
       </c>
-      <c r="M18" s="2"/>
+      <c r="L18" t="s">
+        <v>179</v>
+      </c>
+      <c r="M18">
+        <v>40.080220679999996</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="3"/>
@@ -1677,7 +1779,12 @@
       <c r="K19">
         <v>-24.587215736342099</v>
       </c>
-      <c r="M19" s="2"/>
+      <c r="L19" t="s">
+        <v>179</v>
+      </c>
+      <c r="M19">
+        <v>40.080220679999996</v>
+      </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="3"/>
@@ -1717,7 +1824,12 @@
       <c r="K20">
         <v>-14.245037794730999</v>
       </c>
-      <c r="M20" s="2"/>
+      <c r="L20" t="s">
+        <v>179</v>
+      </c>
+      <c r="M20">
+        <v>40.080220679999996</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="3"/>
@@ -1757,7 +1869,12 @@
       <c r="K21">
         <v>-11.5581021077878</v>
       </c>
-      <c r="M21" s="2"/>
+      <c r="L21" t="s">
+        <v>180</v>
+      </c>
+      <c r="M21">
+        <v>22.382275700000001</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="3"/>
@@ -1797,7 +1914,12 @@
       <c r="K22">
         <v>-20.997247394466999</v>
       </c>
-      <c r="M22" s="2"/>
+      <c r="L22" t="s">
+        <v>180</v>
+      </c>
+      <c r="M22">
+        <v>36.49892423</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="3"/>
@@ -1837,7 +1959,12 @@
       <c r="K23">
         <v>-2.8997847972639401</v>
       </c>
-      <c r="M23" s="2"/>
+      <c r="L23" t="s">
+        <v>180</v>
+      </c>
+      <c r="M23">
+        <v>40.167833700000003</v>
+      </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="3"/>
@@ -1877,7 +2004,12 @@
       <c r="K24">
         <v>-18.834951228130599</v>
       </c>
-      <c r="M24" s="2"/>
+      <c r="L24" t="s">
+        <v>179</v>
+      </c>
+      <c r="M24">
+        <v>37.796692149999998</v>
+      </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" s="3"/>
@@ -1917,7 +2049,12 @@
       <c r="K25">
         <v>-18.9786169878472</v>
       </c>
-      <c r="M25" s="2"/>
+      <c r="L25" t="s">
+        <v>179</v>
+      </c>
+      <c r="M25">
+        <v>37.796692149999998</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="3"/>
@@ -1957,7 +2094,12 @@
       <c r="K26">
         <v>-3.1960799492499499</v>
       </c>
-      <c r="M26" s="2"/>
+      <c r="L26" t="s">
+        <v>179</v>
+      </c>
+      <c r="M26">
+        <v>38.141782509999999</v>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" s="3"/>
@@ -1997,7 +2139,12 @@
       <c r="K27">
         <v>-24.559755768869699</v>
       </c>
-      <c r="M27" s="2"/>
+      <c r="L27" t="s">
+        <v>180</v>
+      </c>
+      <c r="M27">
+        <v>29.243584739999999</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="3"/>
@@ -2037,7 +2184,12 @@
       <c r="K28">
         <v>-25.185969004111499</v>
       </c>
-      <c r="M28" s="2"/>
+      <c r="L28" t="s">
+        <v>180</v>
+      </c>
+      <c r="M28">
+        <v>29.243584739999999</v>
+      </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="3"/>
@@ -2077,7 +2229,12 @@
       <c r="K29">
         <v>-12.594444749493499</v>
       </c>
-      <c r="M29" s="2"/>
+      <c r="L29" t="s">
+        <v>180</v>
+      </c>
+      <c r="M29">
+        <v>32.712398839999999</v>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="3"/>
@@ -2117,7 +2274,12 @@
       <c r="K30">
         <v>-30.013000542669801</v>
       </c>
-      <c r="M30" s="2"/>
+      <c r="L30" t="s">
+        <v>180</v>
+      </c>
+      <c r="M30">
+        <v>48.220018209999999</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="3"/>
@@ -2157,7 +2319,12 @@
       <c r="K31">
         <v>-14.800622413611199</v>
       </c>
-      <c r="M31" s="2"/>
+      <c r="L31" t="s">
+        <v>180</v>
+      </c>
+      <c r="M31">
+        <v>60.15740684</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="3"/>
@@ -2197,7 +2364,12 @@
       <c r="K32">
         <v>-26.222528229874001</v>
       </c>
-      <c r="M32" s="2"/>
+      <c r="L32" t="s">
+        <v>179</v>
+      </c>
+      <c r="M32">
+        <v>22.965563970000002</v>
+      </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="3"/>
@@ -2237,7 +2409,12 @@
       <c r="K33">
         <v>-23.938608813395099</v>
       </c>
-      <c r="M33" s="2"/>
+      <c r="L33" t="s">
+        <v>180</v>
+      </c>
+      <c r="M33">
+        <v>38.796142289999999</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="3"/>
@@ -2277,7 +2454,12 @@
       <c r="K34">
         <v>-24.269407722398199</v>
       </c>
-      <c r="M34" s="2"/>
+      <c r="L34" t="s">
+        <v>180</v>
+      </c>
+      <c r="M34">
+        <v>49.75050822</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="3"/>
@@ -2317,7 +2499,12 @@
       <c r="K35">
         <v>-20.706924830305901</v>
       </c>
-      <c r="M35" s="2"/>
+      <c r="L35" t="s">
+        <v>179</v>
+      </c>
+      <c r="M35">
+        <v>49.205664730000002</v>
+      </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="3"/>
@@ -2357,7 +2544,12 @@
       <c r="K36">
         <v>-20.072421872992301</v>
       </c>
-      <c r="M36" s="2"/>
+      <c r="L36" t="s">
+        <v>179</v>
+      </c>
+      <c r="M36">
+        <v>49.205664730000002</v>
+      </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="3"/>
@@ -2397,7 +2589,12 @@
       <c r="K37">
         <v>-14.216965905065599</v>
       </c>
-      <c r="M37" s="2"/>
+      <c r="L37" t="s">
+        <v>180</v>
+      </c>
+      <c r="M37">
+        <v>25.917027730000001</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="3"/>
@@ -2437,7 +2634,12 @@
       <c r="K38">
         <v>-15.206307514732201</v>
       </c>
-      <c r="M38" s="2"/>
+      <c r="L38" t="s">
+        <v>179</v>
+      </c>
+      <c r="M38">
+        <v>33.835054790000001</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="3"/>
@@ -2477,7 +2679,12 @@
       <c r="K39">
         <v>-29.23538743225</v>
       </c>
-      <c r="M39" s="2"/>
+      <c r="L39" t="s">
+        <v>180</v>
+      </c>
+      <c r="M39">
+        <v>32.066366870000003</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="3"/>
@@ -2517,7 +2724,12 @@
       <c r="K40">
         <v>-28.855004473638399</v>
       </c>
-      <c r="M40" s="2"/>
+      <c r="L40" t="s">
+        <v>180</v>
+      </c>
+      <c r="M40">
+        <v>29.038241719999998</v>
+      </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="3"/>
@@ -2557,7 +2769,12 @@
       <c r="K41">
         <v>-20.745815555081201</v>
       </c>
-      <c r="M41" s="2"/>
+      <c r="L41" t="s">
+        <v>180</v>
+      </c>
+      <c r="M41">
+        <v>45.298557350000003</v>
+      </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="3"/>
@@ -2597,6 +2814,12 @@
       <c r="K42">
         <v>-24.4348233487272</v>
       </c>
+      <c r="L42" t="s">
+        <v>179</v>
+      </c>
+      <c r="M42">
+        <v>52.203558819999998</v>
+      </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
@@ -2632,6 +2855,12 @@
       <c r="K43">
         <v>-23.677945615534199</v>
       </c>
+      <c r="L43" t="s">
+        <v>180</v>
+      </c>
+      <c r="M43">
+        <v>35.102705739999998</v>
+      </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
@@ -2667,6 +2896,12 @@
       <c r="K44">
         <v>-27.9161148725419</v>
       </c>
+      <c r="L44" t="s">
+        <v>180</v>
+      </c>
+      <c r="M44">
+        <v>19.132380090000002</v>
+      </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
@@ -2702,6 +2937,12 @@
       <c r="K45">
         <v>-26.240087328857999</v>
       </c>
+      <c r="L45" t="s">
+        <v>180</v>
+      </c>
+      <c r="M45">
+        <v>54.16401432</v>
+      </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
@@ -2737,6 +2978,12 @@
       <c r="K46">
         <v>-22.7103654762908</v>
       </c>
+      <c r="L46" t="s">
+        <v>180</v>
+      </c>
+      <c r="M46">
+        <v>50.747106369999997</v>
+      </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
@@ -2772,6 +3019,12 @@
       <c r="K47">
         <v>-18.768227131914198</v>
       </c>
+      <c r="L47" t="s">
+        <v>179</v>
+      </c>
+      <c r="M47">
+        <v>32.463249300000001</v>
+      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
@@ -2807,8 +3060,14 @@
       <c r="K48">
         <v>-18.152302369396001</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L48" t="s">
+        <v>179</v>
+      </c>
+      <c r="M48">
+        <v>32.463249300000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>85</v>
       </c>
@@ -2842,8 +3101,14 @@
       <c r="K49">
         <v>-18.9251582426363</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L49" t="s">
+        <v>180</v>
+      </c>
+      <c r="M49">
+        <v>30.034839869999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>139</v>
       </c>
@@ -2877,8 +3142,14 @@
       <c r="K50">
         <v>6.9282036429999998</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L50" t="s">
+        <v>180</v>
+      </c>
+      <c r="M50">
+        <v>20.413720560000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>140</v>
       </c>
@@ -2912,8 +3183,14 @@
       <c r="K51">
         <v>-16.724423049999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L51" t="s">
+        <v>180</v>
+      </c>
+      <c r="M51">
+        <v>20.05516883</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>141</v>
       </c>
@@ -2947,8 +3224,14 @@
       <c r="K52">
         <v>-11.40567523</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L52" t="s">
+        <v>180</v>
+      </c>
+      <c r="M52">
+        <v>45.68471632</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>142</v>
       </c>
@@ -2982,8 +3265,14 @@
       <c r="K53">
         <v>9.7516370919999993</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L53" t="s">
+        <v>180</v>
+      </c>
+      <c r="M53">
+        <v>20.619177669999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>143</v>
       </c>
@@ -3017,8 +3306,14 @@
       <c r="K54">
         <v>-23.905274769999998</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L54" t="s">
+        <v>179</v>
+      </c>
+      <c r="M54">
+        <v>41.380612419999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>143</v>
       </c>
@@ -3052,8 +3347,14 @@
       <c r="K55">
         <v>-5.454652812</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L55" t="s">
+        <v>179</v>
+      </c>
+      <c r="M55">
+        <v>41.380612419999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>144</v>
       </c>
@@ -3087,8 +3388,14 @@
       <c r="K56">
         <v>-18.296058599999999</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L56" t="s">
+        <v>179</v>
+      </c>
+      <c r="M56">
+        <v>23.389825479999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>144</v>
       </c>
@@ -3122,8 +3429,14 @@
       <c r="K57">
         <v>-2.0088620129999999</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L57" t="s">
+        <v>179</v>
+      </c>
+      <c r="M57">
+        <v>23.389825479999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>144</v>
       </c>
@@ -3157,8 +3470,14 @@
       <c r="K58">
         <v>-6.683671554</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L58" t="s">
+        <v>179</v>
+      </c>
+      <c r="M58">
+        <v>23.389825479999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>145</v>
       </c>
@@ -3192,8 +3511,14 @@
       <c r="K59">
         <v>-6.3487596709999998</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L59" t="s">
+        <v>179</v>
+      </c>
+      <c r="M59">
+        <v>21.454125229999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>146</v>
       </c>
@@ -3227,8 +3552,14 @@
       <c r="K60">
         <v>-2.7081418959999999</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L60" t="s">
+        <v>179</v>
+      </c>
+      <c r="M60">
+        <v>42.746828020000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>147</v>
       </c>
@@ -3262,8 +3593,14 @@
       <c r="K61">
         <v>-19.996739399999999</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L61" t="s">
+        <v>180</v>
+      </c>
+      <c r="M61">
+        <v>48.734630639999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>148</v>
       </c>
@@ -3296,6 +3633,12 @@
       </c>
       <c r="K62">
         <v>-15.88274822</v>
+      </c>
+      <c r="L62" t="s">
+        <v>180</v>
+      </c>
+      <c r="M62">
+        <v>38.086910289999999</v>
       </c>
     </row>
   </sheetData>
